--- a/data/trans_dic/P1803_2016_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1803_2016_2023-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,03</t>
+          <t>3,28; 7,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,85</t>
+          <t>2,57; 10,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,33</t>
+          <t>2,89; 7,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,22</t>
+          <t>2,65; 9,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,74</t>
+          <t>3,66; 6,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,13</t>
+          <t>3,25; 8,32</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,66</t>
+          <t>2,99; 6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 11,69</t>
+          <t>4,76; 11,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 9,73</t>
+          <t>4,93; 9,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 13,69</t>
+          <t>7,19; 12,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,29</t>
+          <t>4,52; 7,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,59</t>
+          <t>6,65; 10,89</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,18</t>
+          <t>4,23; 8,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,18</t>
+          <t>8,51; 13,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,35</t>
+          <t>3,15; 6,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 13,39</t>
+          <t>7,97; 12,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 6,59</t>
+          <t>4,04; 6,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,98</t>
+          <t>8,99; 12,45</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,94</t>
+          <t>3,18; 6,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 73,16</t>
+          <t>8,22; 13,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,45</t>
+          <t>3,72; 7,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,64</t>
+          <t>9,53; 13,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,47</t>
+          <t>3,91; 6,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 49,34</t>
+          <t>9,4; 12,35</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,06</t>
+          <t>2,98; 7,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,5</t>
+          <t>5,7; 9,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,06</t>
+          <t>4,13; 9,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,35; 15,45</t>
+          <t>10,96; 15,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,18</t>
+          <t>4,17; 7,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 12,36</t>
+          <t>8,99; 11,81</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,16</t>
+          <t>0,89; 3,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,77</t>
+          <t>4,7; 8,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,54; 10,36</t>
+          <t>4,6; 10,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,58</t>
+          <t>9,04; 13,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 6,82</t>
+          <t>3,1; 6,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,65; 9,18</t>
+          <t>7,3; 10,52</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,02</t>
+          <t>1,27; 4,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,2</t>
+          <t>1,83; 5,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,15</t>
+          <t>2,12; 6,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,19</t>
+          <t>5,05; 8,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,84</t>
+          <t>2,08; 4,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 6,45</t>
+          <t>4,3; 6,77</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,33</t>
+          <t>3,9; 5,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,04; 33,89</t>
+          <t>7,07; 9,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,37</t>
+          <t>4,79; 6,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,6</t>
+          <t>9,03; 10,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 5,62</t>
+          <t>4,54; 5,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,36</t>
+          <t>8,4; 9,69</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>41168</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12974; 33697</t>
+          <t>13740; 32963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7451; 39418</t>
+          <t>10493; 40787</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11597; 29021</t>
+          <t>11438; 28646</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7689; 28864</t>
+          <t>9622; 33842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28936; 54980</t>
+          <t>29817; 55188</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19508; 57965</t>
+          <t>25046; 64094</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50801</t>
+          <t>48639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84335</t>
+          <t>84027</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17448; 39312</t>
+          <t>17665; 39525</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21836; 49531</t>
+          <t>22683; 52889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29385; 54806</t>
+          <t>27772; 52694</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32075; 70011</t>
+          <t>36037; 64568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49952; 84075</t>
+          <t>52154; 84447</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60312; 108383</t>
+          <t>65071; 106502</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69512</t>
+          <t>69075</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59628</t>
+          <t>62127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>129140</t>
+          <t>131203</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29079; 54756</t>
+          <t>28301; 55065</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55404; 86787</t>
+          <t>52803; 85463</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20349; 42020</t>
+          <t>20812; 43232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48779; 72622</t>
+          <t>49569; 76483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56147; 87686</t>
+          <t>53719; 87966</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110892; 150867</t>
+          <t>111791; 154691</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>314059</t>
+          <t>72711</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76588</t>
+          <t>83439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>390647</t>
+          <t>156149</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20781; 44804</t>
+          <t>20531; 43595</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88961; 649477</t>
+          <t>57558; 92393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24049; 48333</t>
+          <t>24161; 47437</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61238; 90100</t>
+          <t>70200; 96921</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50306; 83838</t>
+          <t>50666; 84511</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>161706; 789746</t>
+          <t>135083; 177587</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72436</t>
+          <t>79423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>117893</t>
+          <t>125400</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13987; 33746</t>
+          <t>14234; 34387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34677; 58954</t>
+          <t>34747; 58890</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20438; 45031</t>
+          <t>20513; 45633</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62048; 84481</t>
+          <t>66619; 91456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40540; 69962</t>
+          <t>40671; 71365</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102973; 136970</t>
+          <t>109424; 143665</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67177</t>
+          <t>73939</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2980; 13904</t>
+          <t>2967; 13290</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16564; 32296</t>
+          <t>19120; 35603</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17159; 39142</t>
+          <t>17384; 39381</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17935; 70424</t>
+          <t>39709; 58224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23386; 48538</t>
+          <t>22096; 46709</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35615; 89647</t>
+          <t>61812; 89009</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36497</t>
+          <t>40917</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3289; 12890</t>
+          <t>3262; 12487</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5033; 14696</t>
+          <t>5681; 16581</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7590; 24628</t>
+          <t>8500; 24999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20390; 34813</t>
+          <t>23437; 39767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13434; 31836</t>
+          <t>13640; 32757</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29284; 45641</t>
+          <t>33262; 52402</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>345891</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>860399</t>
+          <t>652803</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>130818; 180874</t>
+          <t>132226; 181067</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>278006; 1172526</t>
+          <t>249779; 322394</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>166982; 225840</t>
+          <t>169707; 223109</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>283016; 387944</t>
+          <t>337119; 401514</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>312431; 390129</t>
+          <t>315049; 391061</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>619385; 1663521</t>
+          <t>610512; 704185</t>
         </is>
       </c>
     </row>
